--- a/tests/evals/timesheets/06-xlsx-priya-07/input.xlsx
+++ b/tests/evals/timesheets/06-xlsx-priya-07/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,159 +461,152 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03  8.00</t>
+          <t>2026-07-06  8.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06  8.00</t>
+          <t>2026-07-07  8.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07  8.00</t>
+          <t>2026-07-08  8.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08  8.00</t>
+          <t>2026-07-09  8.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09  8.00</t>
+          <t>2026-07-10  8.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10  8.00</t>
+          <t>2026-07-13  8.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13  8.00</t>
+          <t>2026-07-14  8.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14  8.00</t>
+          <t>2026-07-15  8.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15  8.00</t>
+          <t>2026-07-16  8.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16  8.00</t>
+          <t>2026-07-17  8.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17  8.00</t>
+          <t>2026-07-20  8.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20  8.00</t>
+          <t>2026-07-21  8.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21  8.00</t>
+          <t>2026-07-22  8.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22  8.00</t>
+          <t>2026-07-23  8.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23  8.00</t>
+          <t>2026-07-24  8.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24  8.00</t>
+          <t>2026-07-27  8.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27  8.00</t>
+          <t>2026-07-28  8.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28  8.00</t>
+          <t>2026-07-29  8.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29  8.00</t>
+          <t>2026-07-30  8.00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30  8.00</t>
+          <t>2026-07-31  8.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31  8.00</t>
+          <t>Total: 176.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
-        <is>
-          <t>Total: 184.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
         <is>
           <t>Approved by Lee Fontaine on 2026-07-31</t>
         </is>
